--- a/data/trans_orig/IP31B_2023-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/IP31B_2023-Habitat-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>22651</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>15473</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>32152</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>18,83%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>12,86%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>26,73%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>40</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>27849</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>21299</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>37212</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>24,38%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>18,64%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>32,57%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>23502</t>
+          <t>30255</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>15347</t>
+          <t>22397</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>33743</t>
+          <t>40429</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>25,51%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>25,37%</t>
+          <t>34,09%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>51351</t>
+          <t>52906</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>40093</t>
+          <t>42136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>63433</t>
+          <t>65866</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>27,57%</t>
         </is>
       </c>
     </row>
@@ -833,72 +833,72 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>63881</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>52440</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>76101</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>53,1%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>43,59%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>63,26%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>88</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>51896</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>43646</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>60419</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>45,42%</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>38,2%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>52,88%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>66781</t>
+          <t>53236</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>52073</t>
+          <t>44702</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>83595</t>
+          <t>62228</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>50,21%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>39,15%</t>
+          <t>37,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>62,85%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>118676</t>
+          <t>117117</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>102801</t>
+          <t>103422</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>138883</t>
+          <t>132388</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>48,0%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>41,58%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>56,17%</t>
+          <t>55,42%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>24992</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>17865</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>33998</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>20,77%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>14,85%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>28,26%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>45</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>26979</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>20457</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>34566</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>23,61%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>17,91%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>30,25%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>31891</t>
+          <t>28336</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>22745</t>
+          <t>21002</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>48449</t>
+          <t>37961</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>23,89%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,71%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>36,43%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>58870</t>
+          <t>53329</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>46659</t>
+          <t>42978</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>75714</t>
+          <t>65079</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>23,81%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>17,99%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>30,62%</t>
+          <t>27,24%</t>
         </is>
       </c>
     </row>
@@ -1059,72 +1059,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>6680</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>3587</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>11864</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>5,55%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>2,98%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>9,86%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>6</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>3353</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1333</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>7265</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2,94%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,17%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>6,36%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8185</t>
+          <t>3074</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4183</t>
+          <t>910</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>14529</t>
+          <t>6366</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>10,92%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>9753</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>6930</t>
+          <t>5725</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>18574</t>
+          <t>15315</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>6,41%</t>
         </is>
       </c>
     </row>
@@ -1172,72 +1172,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2099</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>775</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>4654</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1,74%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>0,64%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>3,87%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>4174</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1945</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>8020</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>3,65%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,02%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2642</t>
+          <t>3697</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1004</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>5563</t>
+          <t>6989</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>5,89%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1247,32 +1247,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>6816</t>
+          <t>5796</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3897</t>
+          <t>3306</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>11644</t>
+          <t>9937</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,16%</t>
         </is>
       </c>
     </row>
@@ -1285,57 +1285,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>120303</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>120303</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>120303</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>188</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>114251</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>161</t>
-        </is>
-      </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>133000</t>
+          <t>118598</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1360,17 +1360,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>247251</t>
+          <t>238901</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>247251</t>
+          <t>238901</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>247251</t>
+          <t>238901</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>46448</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35406</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>59029</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>20,09%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>15,31%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>25,53%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>62</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>44039</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>34354</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>55278</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>23,76%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>18,54%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>29,83%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>46695</t>
+          <t>44614</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>35694</t>
+          <t>35468</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58743</t>
+          <t>56443</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,87%</t>
+          <t>24,8%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>14,42%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>31,37%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>90734</t>
+          <t>91062</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>76405</t>
+          <t>77369</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>107364</t>
+          <t>107597</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>26,17%</t>
         </is>
       </c>
     </row>
@@ -1515,72 +1515,72 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>109350</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>94636</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>122582</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>47,29%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>40,93%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>53,01%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>115</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>76860</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>63922</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>88625</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>41,47%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>34,49%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>47,82%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>153</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>113223</t>
+          <t>78928</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>98637</t>
+          <t>67600</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>127856</t>
+          <t>91375</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45,74%</t>
+          <t>43,87%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>37,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>51,65%</t>
+          <t>50,79%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>190082</t>
+          <t>188278</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>170486</t>
+          <t>170737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>208360</t>
+          <t>206308</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>43,91%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>39,39%</t>
+          <t>41,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>48,14%</t>
+          <t>50,18%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46174</t>
+          <t>53019</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>36731</t>
+          <t>41812</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>56047</t>
+          <t>68497</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>18,08%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>30,24%</t>
+          <t>29,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>59737</t>
+          <t>44991</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>46873</t>
+          <t>35386</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>77235</t>
+          <t>56227</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>25,01%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>31,2%</t>
+          <t>31,25%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>105911</t>
+          <t>98011</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>91018</t>
+          <t>81888</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>124975</t>
+          <t>114990</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>19,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>27,97%</t>
         </is>
       </c>
     </row>
@@ -1741,72 +1741,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>14553</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>9188</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>22465</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>6,29%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>3,97%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>9,71%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>13072</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>6045</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>35430</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>7,05%</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>3,26%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>19,12%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17138</t>
+          <t>7250</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10929</t>
+          <t>4060</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26336</t>
+          <t>12643</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>7,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1816,32 +1816,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>30210</t>
+          <t>21802</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>20625</t>
+          <t>15313</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>52265</t>
+          <t>31232</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>7,6%</t>
         </is>
       </c>
     </row>
@@ -1854,72 +1854,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>7871</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>4844</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>12269</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>3,4%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,09%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>5,31%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>5183</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2270</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>10343</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2,8%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,22%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>5,58%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>10727</t>
+          <t>4132</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>5967</t>
+          <t>1831</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>16481</t>
+          <t>9542</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>6,66%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1929,32 +1929,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>15909</t>
+          <t>12003</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>10472</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>23455</t>
+          <t>18963</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>2,92%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>4,61%</t>
         </is>
       </c>
     </row>
@@ -1967,57 +1967,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>324</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>231241</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>267</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>185327</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>185327</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>185327</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>324</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>179915</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>179915</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>247520</t>
+          <t>179915</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2042,17 +2042,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>432847</t>
+          <t>411156</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>432847</t>
+          <t>411156</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>432847</t>
+          <t>411156</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2084,72 +2084,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>16922</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>10648</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>25791</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10,18%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>6,41%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>15,52%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>26</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>17177</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>9927</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>26223</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>9,23%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>5,33%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>14,08%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>17020</t>
+          <t>17567</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>10997</t>
+          <t>11305</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>25451</t>
+          <t>24363</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>9,32%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>6,02%</t>
+          <t>7,38%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>34198</t>
+          <t>34489</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>23803</t>
+          <t>25065</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>45300</t>
+          <t>46427</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>7,85%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>14,53%</t>
         </is>
       </c>
     </row>
@@ -2197,72 +2197,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>84365</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>70993</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>97346</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>50,75%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>42,71%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>58,56%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>116</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>90156</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>54452</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>111073</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>48,42%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>29,25%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>59,66%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>91836</t>
+          <t>82484</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>78092</t>
+          <t>71210</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>106449</t>
+          <t>93217</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>50,27%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,74%</t>
+          <t>46,46%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>58,27%</t>
+          <t>60,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>181993</t>
+          <t>166849</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>137360</t>
+          <t>150046</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>204475</t>
+          <t>183901</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>49,34%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>37,24%</t>
+          <t>46,96%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>55,43%</t>
+          <t>57,56%</t>
         </is>
       </c>
     </row>
@@ -2310,72 +2310,72 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>50432</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>40305</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>63237</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>30,34%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>24,25%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>38,04%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
           <t>66</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>71337</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>47415</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>117108</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
-        <is>
-          <t>38,31%</t>
-        </is>
-      </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>25,47%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>62,9%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>57299</t>
+          <t>46283</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>45245</t>
+          <t>36600</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>71725</t>
+          <t>57302</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>24,77%</t>
+          <t>23,88%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>39,26%</t>
+          <t>37,39%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2385,32 +2385,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>128636</t>
+          <t>96715</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>102940</t>
+          <t>81936</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>192472</t>
+          <t>114070</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>34,87%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>27,91%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>52,18%</t>
+          <t>35,7%</t>
         </is>
       </c>
     </row>
@@ -2423,72 +2423,72 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>9450</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>5399</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>15268</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>9,19%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>1977</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>373</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>7351</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>3,95%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>11230</t>
+          <t>1503</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>6040</t>
+          <t>354</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17888</t>
+          <t>4614</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>3,01%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2498,32 +2498,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>13207</t>
+          <t>10953</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>7833</t>
+          <t>6541</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21661</t>
+          <t>17195</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,38%</t>
         </is>
       </c>
     </row>
@@ -2536,72 +2536,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>5055</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>2389</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>10783</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>3,04%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>1,44%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>6,49%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>5539</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>2414</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>11451</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>6,15%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5436</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2699</t>
+          <t>2480</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>9852</t>
+          <t>10669</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2611,32 +2611,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>10491</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>6417</t>
+          <t>6024</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>18286</t>
+          <t>17874</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,28%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,89%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,59%</t>
         </is>
       </c>
     </row>
@@ -2654,17 +2654,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>186186</t>
+          <t>166223</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>186186</t>
+          <t>166223</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>186186</t>
+          <t>166223</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2689,17 +2689,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>182693</t>
+          <t>153273</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>182693</t>
+          <t>153273</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>182693</t>
+          <t>153273</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2724,17 +2724,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>368880</t>
+          <t>319496</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>368880</t>
+          <t>319496</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>368880</t>
+          <t>319496</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2766,72 +2766,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>26646</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>19035</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>35255</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>16,13%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>11,52%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>21,34%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>47</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>32931</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>25042</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>42267</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>20,15%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>15,32%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>25,86%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>37</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>28067</t>
+          <t>34178</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>20460</t>
+          <t>25948</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>38381</t>
+          <t>43346</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>26,63%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>60998</t>
+          <t>60824</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>49942</t>
+          <t>48901</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>73978</t>
+          <t>72140</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>14,7%</t>
+          <t>14,91%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,77%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -2879,72 +2879,72 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>86867</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>75893</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>97506</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>52,58%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>45,93%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>59,02%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>125</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>88564</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>77868</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>99269</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>54,19%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>47,64%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>60,74%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>119</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>93279</t>
+          <t>89511</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>81272</t>
+          <t>78007</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>105075</t>
+          <t>99436</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>54,99%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>46,09%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>61,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2954,32 +2954,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>181843</t>
+          <t>176378</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>165219</t>
+          <t>161930</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>197608</t>
+          <t>191596</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>53,52%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>48,63%</t>
+          <t>49,37%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>58,41%</t>
         </is>
       </c>
     </row>
@@ -2992,72 +2992,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>38153</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>29774</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>47754</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>23,09%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>18,02%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>28,9%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>39</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>27641</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>20349</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>36775</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>16,91%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>12,45%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>22,5%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>55</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>40670</t>
+          <t>25533</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>31746</t>
+          <t>18364</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>50105</t>
+          <t>33726</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>15,68%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>28,41%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3067,32 +3067,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>68311</t>
+          <t>63686</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>56568</t>
+          <t>52287</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>83583</t>
+          <t>75567</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,42%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,94%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>24,6%</t>
+          <t>23,04%</t>
         </is>
       </c>
     </row>
@@ -3110,32 +3110,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>6267</t>
+          <t>6353</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3156</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>11250</t>
+          <t>11403</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>6,88%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3145,32 +3145,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>6734</t>
+          <t>6325</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3222</t>
+          <t>3023</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12048</t>
+          <t>11012</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>6,83%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3180,32 +3180,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>13001</t>
+          <t>12678</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>8301</t>
+          <t>8154</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>20144</t>
+          <t>19110</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>3,83%</t>
+          <t>3,87%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,83%</t>
         </is>
       </c>
     </row>
@@ -3218,72 +3218,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>7202</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3732</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>14098</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>4,36%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>8,53%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>13</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>8032</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>4256</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>12962</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>4,91%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>7,93%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>7588</t>
+          <t>7244</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3812</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>14520</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>4,3%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3293,32 +3293,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>15620</t>
+          <t>14446</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9774</t>
+          <t>9643</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>23850</t>
+          <t>22360</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,4%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,82%</t>
         </is>
       </c>
     </row>
@@ -3331,57 +3331,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>231</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>165221</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>165221</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>165221</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>163435</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>163435</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>163435</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>231</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>176339</t>
+          <t>162791</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>176339</t>
+          <t>162791</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>176339</t>
+          <t>162791</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3406,17 +3406,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>339773</t>
+          <t>328012</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>339773</t>
+          <t>328012</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>339773</t>
+          <t>328012</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3448,72 +3448,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>112666</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>95658</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>130745</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>16,5%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>14,01%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>19,14%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>175</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>121996</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>100409</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>140216</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>18,79%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>15,47%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>21,6%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>148</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>115285</t>
+          <t>126614</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>98810</t>
+          <t>109025</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>134867</t>
+          <t>144966</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>15,59%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>17,74%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>23,59%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3523,32 +3523,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>237281</t>
+          <t>239281</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>212258</t>
+          <t>213495</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>266073</t>
+          <t>264840</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>16,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>19,16%</t>
+          <t>20,41%</t>
         </is>
       </c>
     </row>
@@ -3561,72 +3561,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>440</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>344463</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>319036</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>371426</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>50,43%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>46,71%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>54,38%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>444</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>307476</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>265085</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>333648</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>47,36%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>40,83%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>51,39%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>440</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>365120</t>
+          <t>304158</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>337665</t>
+          <t>282669</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>395340</t>
+          <t>326544</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>49,37%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>45,66%</t>
+          <t>45,99%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,46%</t>
+          <t>53,13%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3636,32 +3636,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>672595</t>
+          <t>648622</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>620907</t>
+          <t>613763</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>712488</t>
+          <t>686937</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>48,43%</t>
+          <t>49,99%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>44,71%</t>
+          <t>47,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>51,3%</t>
+          <t>52,94%</t>
         </is>
       </c>
     </row>
@@ -3674,72 +3674,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>239</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>166597</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>146588</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>189356</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>24,39%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>21,46%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>27,72%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>219</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>172131</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>144335</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>240155</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>26,51%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>22,23%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>36,99%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>239</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>189597</t>
+          <t>145143</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>165196</t>
+          <t>128779</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>217037</t>
+          <t>163508</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>23,62%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>22,34%</t>
+          <t>20,95%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>26,6%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3749,32 +3749,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>361728</t>
+          <t>311740</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>325266</t>
+          <t>286448</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>432378</t>
+          <t>341675</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>23,42%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>26,33%</t>
         </is>
       </c>
     </row>
@@ -3787,72 +3787,72 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>37035</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>28583</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>48799</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>5,42%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>4,19%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>7,14%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>32</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>24669</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>16092</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>47211</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>3,8%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>2,48%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>7,27%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>43287</t>
+          <t>18152</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>32460</t>
+          <t>11723</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>55268</t>
+          <t>25020</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>4,39%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>7,47%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3862,32 +3862,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>67956</t>
+          <t>55186</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>53014</t>
+          <t>43681</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>91551</t>
+          <t>67970</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>5,24%</t>
         </is>
       </c>
     </row>
@@ -3900,72 +3900,72 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>22227</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>15446</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>30452</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>3,25%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>2,26%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>4,46%</t>
+        </is>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
           <t>38</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>22927</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>16404</t>
-        </is>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>32428</t>
-        </is>
-      </c>
-      <c r="G32" s="2" t="inlineStr">
-        <is>
-          <t>3,53%</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>2,53%</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="inlineStr">
-        <is>
-          <t>5,0%</t>
-        </is>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>26264</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>18904</t>
+          <t>14809</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>36147</t>
+          <t>28927</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>4,89%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3975,32 +3975,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>49192</t>
+          <t>42736</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>38916</t>
+          <t>34292</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>61916</t>
+          <t>55663</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>3,54%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,29%</t>
         </is>
       </c>
     </row>
@@ -4013,57 +4013,57 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>935</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>682988</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
           <t>908</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>649199</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>935</t>
-        </is>
-      </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>739553</t>
+          <t>614576</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4088,17 +4088,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1388752</t>
+          <t>1297565</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
